--- a/sipii_caixa_20260707.xlsx
+++ b/sipii_caixa_20260707.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW172"/>
+  <dimension ref="A1:BB172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -517,6 +517,11 @@
     <col width="15" customWidth="1" min="47" max="47"/>
     <col width="15" customWidth="1" min="48" max="48"/>
     <col width="15" customWidth="1" min="49" max="49"/>
+    <col width="15" customWidth="1" min="50" max="50"/>
+    <col width="15" customWidth="1" min="51" max="51"/>
+    <col width="15" customWidth="1" min="52" max="52"/>
+    <col width="15" customWidth="1" min="53" max="53"/>
+    <col width="15" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -763,6 +768,31 @@
       <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>doc_raio_x</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Data Base Consulta</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Data Rentabilidade Ref</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Fallback Rentabilidade</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Dias Úteis Fallback</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Alerta Rentabilidade Defasada</t>
         </is>
       </c>
     </row>
@@ -1000,6 +1030,11 @@
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" s="2" t="inlineStr"/>
+      <c r="AX2" s="2" t="inlineStr"/>
+      <c r="AY2" s="2" t="inlineStr"/>
+      <c r="AZ2" s="2" t="inlineStr"/>
+      <c r="BA2" s="2" t="inlineStr"/>
+      <c r="BB2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1235,6 +1270,11 @@
       </c>
       <c r="AV3" s="4" t="inlineStr"/>
       <c r="AW3" s="4" t="inlineStr"/>
+      <c r="AX3" s="4" t="inlineStr"/>
+      <c r="AY3" s="4" t="inlineStr"/>
+      <c r="AZ3" s="4" t="inlineStr"/>
+      <c r="BA3" s="4" t="inlineStr"/>
+      <c r="BB3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1469,6 +1509,11 @@
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" s="2" t="inlineStr"/>
+      <c r="AX4" s="2" t="inlineStr"/>
+      <c r="AY4" s="2" t="inlineStr"/>
+      <c r="AZ4" s="2" t="inlineStr"/>
+      <c r="BA4" s="2" t="inlineStr"/>
+      <c r="BB4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1704,6 +1749,11 @@
       </c>
       <c r="AV5" s="4" t="inlineStr"/>
       <c r="AW5" s="4" t="inlineStr"/>
+      <c r="AX5" s="4" t="inlineStr"/>
+      <c r="AY5" s="4" t="inlineStr"/>
+      <c r="AZ5" s="4" t="inlineStr"/>
+      <c r="BA5" s="4" t="inlineStr"/>
+      <c r="BB5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1942,6 +1992,11 @@
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" s="2" t="inlineStr"/>
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr"/>
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2173,6 +2228,11 @@
       </c>
       <c r="AV7" s="4" t="inlineStr"/>
       <c r="AW7" s="4" t="inlineStr"/>
+      <c r="AX7" s="4" t="inlineStr"/>
+      <c r="AY7" s="4" t="inlineStr"/>
+      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2408,6 +2468,11 @@
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" s="2" t="inlineStr"/>
+      <c r="AX8" s="2" t="inlineStr"/>
+      <c r="AY8" s="2" t="inlineStr"/>
+      <c r="AZ8" s="2" t="inlineStr"/>
+      <c r="BA8" s="2" t="inlineStr"/>
+      <c r="BB8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2639,6 +2704,11 @@
       </c>
       <c r="AV9" s="4" t="inlineStr"/>
       <c r="AW9" s="4" t="inlineStr"/>
+      <c r="AX9" s="4" t="inlineStr"/>
+      <c r="AY9" s="4" t="inlineStr"/>
+      <c r="AZ9" s="4" t="inlineStr"/>
+      <c r="BA9" s="4" t="inlineStr"/>
+      <c r="BB9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2870,6 +2940,11 @@
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" s="2" t="inlineStr"/>
+      <c r="AX10" s="2" t="inlineStr"/>
+      <c r="AY10" s="2" t="inlineStr"/>
+      <c r="AZ10" s="2" t="inlineStr"/>
+      <c r="BA10" s="2" t="inlineStr"/>
+      <c r="BB10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -3109,6 +3184,11 @@
           <t>https://web.microsoftstream.com/video/cec16660-0485-4e14-9a79-ff7c9fd2158f?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX11" s="4" t="inlineStr"/>
+      <c r="AY11" s="4" t="inlineStr"/>
+      <c r="AZ11" s="4" t="inlineStr"/>
+      <c r="BA11" s="4" t="inlineStr"/>
+      <c r="BB11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3348,6 +3428,11 @@
           <t>https://web.microsoftstream.com/video/140b7682-00df-491d-b451-73ae70a040fa?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX12" s="2" t="inlineStr"/>
+      <c r="AY12" s="2" t="inlineStr"/>
+      <c r="AZ12" s="2" t="inlineStr"/>
+      <c r="BA12" s="2" t="inlineStr"/>
+      <c r="BB12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -3584,6 +3669,11 @@
       </c>
       <c r="AV13" s="4" t="inlineStr"/>
       <c r="AW13" s="4" t="inlineStr"/>
+      <c r="AX13" s="4" t="inlineStr"/>
+      <c r="AY13" s="4" t="inlineStr"/>
+      <c r="AZ13" s="4" t="inlineStr"/>
+      <c r="BA13" s="4" t="inlineStr"/>
+      <c r="BB13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3819,6 +3909,11 @@
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" s="2" t="inlineStr"/>
+      <c r="AX14" s="2" t="inlineStr"/>
+      <c r="AY14" s="2" t="inlineStr"/>
+      <c r="AZ14" s="2" t="inlineStr"/>
+      <c r="BA14" s="2" t="inlineStr"/>
+      <c r="BB14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -4058,6 +4153,11 @@
           <t>https://web.microsoftstream.com/video/a5ab94de-1f04-4f00-87d2-ffa0c6babbaf?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX15" s="4" t="inlineStr"/>
+      <c r="AY15" s="4" t="inlineStr"/>
+      <c r="AZ15" s="4" t="inlineStr"/>
+      <c r="BA15" s="4" t="inlineStr"/>
+      <c r="BB15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -4293,6 +4393,11 @@
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" s="2" t="inlineStr"/>
+      <c r="AX16" s="2" t="inlineStr"/>
+      <c r="AY16" s="2" t="inlineStr"/>
+      <c r="AZ16" s="2" t="inlineStr"/>
+      <c r="BA16" s="2" t="inlineStr"/>
+      <c r="BB16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -4524,6 +4629,11 @@
       </c>
       <c r="AV17" s="4" t="inlineStr"/>
       <c r="AW17" s="4" t="inlineStr"/>
+      <c r="AX17" s="4" t="inlineStr"/>
+      <c r="AY17" s="4" t="inlineStr"/>
+      <c r="AZ17" s="4" t="inlineStr"/>
+      <c r="BA17" s="4" t="inlineStr"/>
+      <c r="BB17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4763,6 +4873,11 @@
           <t>https://web.microsoftstream.com/video/2fc898a1-d287-4c38-9f3a-9efa66e9bf47?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX18" s="2" t="inlineStr"/>
+      <c r="AY18" s="2" t="inlineStr"/>
+      <c r="AZ18" s="2" t="inlineStr"/>
+      <c r="BA18" s="2" t="inlineStr"/>
+      <c r="BB18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -4992,6 +5107,11 @@
       </c>
       <c r="AV19" s="4" t="inlineStr"/>
       <c r="AW19" s="4" t="inlineStr"/>
+      <c r="AX19" s="4" t="inlineStr"/>
+      <c r="AY19" s="4" t="inlineStr"/>
+      <c r="AZ19" s="4" t="inlineStr"/>
+      <c r="BA19" s="4" t="inlineStr"/>
+      <c r="BB19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -5227,6 +5347,11 @@
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" s="2" t="inlineStr"/>
+      <c r="AX20" s="2" t="inlineStr"/>
+      <c r="AY20" s="2" t="inlineStr"/>
+      <c r="AZ20" s="2" t="inlineStr"/>
+      <c r="BA20" s="2" t="inlineStr"/>
+      <c r="BB20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -5467,6 +5592,11 @@
       </c>
       <c r="AV21" s="4" t="inlineStr"/>
       <c r="AW21" s="4" t="inlineStr"/>
+      <c r="AX21" s="4" t="inlineStr"/>
+      <c r="AY21" s="4" t="inlineStr"/>
+      <c r="AZ21" s="4" t="inlineStr"/>
+      <c r="BA21" s="4" t="inlineStr"/>
+      <c r="BB21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -5702,6 +5832,11 @@
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" s="2" t="inlineStr"/>
+      <c r="AX22" s="2" t="inlineStr"/>
+      <c r="AY22" s="2" t="inlineStr"/>
+      <c r="AZ22" s="2" t="inlineStr"/>
+      <c r="BA22" s="2" t="inlineStr"/>
+      <c r="BB22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -5937,6 +6072,11 @@
       </c>
       <c r="AV23" s="4" t="inlineStr"/>
       <c r="AW23" s="4" t="inlineStr"/>
+      <c r="AX23" s="4" t="inlineStr"/>
+      <c r="AY23" s="4" t="inlineStr"/>
+      <c r="AZ23" s="4" t="inlineStr"/>
+      <c r="BA23" s="4" t="inlineStr"/>
+      <c r="BB23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -6168,6 +6308,11 @@
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" s="2" t="inlineStr"/>
+      <c r="AX24" s="2" t="inlineStr"/>
+      <c r="AY24" s="2" t="inlineStr"/>
+      <c r="AZ24" s="2" t="inlineStr"/>
+      <c r="BA24" s="2" t="inlineStr"/>
+      <c r="BB24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -6403,6 +6548,11 @@
       </c>
       <c r="AV25" s="4" t="inlineStr"/>
       <c r="AW25" s="4" t="inlineStr"/>
+      <c r="AX25" s="4" t="inlineStr"/>
+      <c r="AY25" s="4" t="inlineStr"/>
+      <c r="AZ25" s="4" t="inlineStr"/>
+      <c r="BA25" s="4" t="inlineStr"/>
+      <c r="BB25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -6638,6 +6788,11 @@
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" s="2" t="inlineStr"/>
+      <c r="AX26" s="2" t="inlineStr"/>
+      <c r="AY26" s="2" t="inlineStr"/>
+      <c r="AZ26" s="2" t="inlineStr"/>
+      <c r="BA26" s="2" t="inlineStr"/>
+      <c r="BB26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -6873,6 +7028,11 @@
       </c>
       <c r="AV27" s="4" t="inlineStr"/>
       <c r="AW27" s="4" t="inlineStr"/>
+      <c r="AX27" s="4" t="inlineStr"/>
+      <c r="AY27" s="4" t="inlineStr"/>
+      <c r="AZ27" s="4" t="inlineStr"/>
+      <c r="BA27" s="4" t="inlineStr"/>
+      <c r="BB27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -7096,6 +7256,11 @@
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" s="2" t="inlineStr"/>
+      <c r="AX28" s="2" t="inlineStr"/>
+      <c r="AY28" s="2" t="inlineStr"/>
+      <c r="AZ28" s="2" t="inlineStr"/>
+      <c r="BA28" s="2" t="inlineStr"/>
+      <c r="BB28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -7323,6 +7488,11 @@
           <t>https://caixa.sharepoint.com/:v:/t/O365GRP-GEICO/EeFPVsuRvYtKt6bMstsCLiUBtcBOAe5vK4jLZ_DjXA4drg?e=XxU8cb</t>
         </is>
       </c>
+      <c r="AX29" s="4" t="inlineStr"/>
+      <c r="AY29" s="4" t="inlineStr"/>
+      <c r="AZ29" s="4" t="inlineStr"/>
+      <c r="BA29" s="4" t="inlineStr"/>
+      <c r="BB29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -7550,6 +7720,11 @@
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" s="2" t="inlineStr"/>
+      <c r="AX30" s="2" t="inlineStr"/>
+      <c r="AY30" s="2" t="inlineStr"/>
+      <c r="AZ30" s="2" t="inlineStr"/>
+      <c r="BA30" s="2" t="inlineStr"/>
+      <c r="BB30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -7773,6 +7948,11 @@
       </c>
       <c r="AV31" s="4" t="inlineStr"/>
       <c r="AW31" s="4" t="inlineStr"/>
+      <c r="AX31" s="4" t="inlineStr"/>
+      <c r="AY31" s="4" t="inlineStr"/>
+      <c r="AZ31" s="4" t="inlineStr"/>
+      <c r="BA31" s="4" t="inlineStr"/>
+      <c r="BB31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -8008,6 +8188,11 @@
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" s="2" t="inlineStr"/>
+      <c r="AX32" s="2" t="inlineStr"/>
+      <c r="AY32" s="2" t="inlineStr"/>
+      <c r="AZ32" s="2" t="inlineStr"/>
+      <c r="BA32" s="2" t="inlineStr"/>
+      <c r="BB32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -8243,6 +8428,11 @@
       </c>
       <c r="AV33" s="4" t="inlineStr"/>
       <c r="AW33" s="4" t="inlineStr"/>
+      <c r="AX33" s="4" t="inlineStr"/>
+      <c r="AY33" s="4" t="inlineStr"/>
+      <c r="AZ33" s="4" t="inlineStr"/>
+      <c r="BA33" s="4" t="inlineStr"/>
+      <c r="BB33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -8466,6 +8656,11 @@
       </c>
       <c r="AV34" s="2" t="inlineStr"/>
       <c r="AW34" s="2" t="inlineStr"/>
+      <c r="AX34" s="2" t="inlineStr"/>
+      <c r="AY34" s="2" t="inlineStr"/>
+      <c r="AZ34" s="2" t="inlineStr"/>
+      <c r="BA34" s="2" t="inlineStr"/>
+      <c r="BB34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -8697,6 +8892,11 @@
       </c>
       <c r="AV35" s="4" t="inlineStr"/>
       <c r="AW35" s="4" t="inlineStr"/>
+      <c r="AX35" s="4" t="inlineStr"/>
+      <c r="AY35" s="4" t="inlineStr"/>
+      <c r="AZ35" s="4" t="inlineStr"/>
+      <c r="BA35" s="4" t="inlineStr"/>
+      <c r="BB35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -8928,6 +9128,11 @@
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" s="2" t="inlineStr"/>
+      <c r="AX36" s="2" t="inlineStr"/>
+      <c r="AY36" s="2" t="inlineStr"/>
+      <c r="AZ36" s="2" t="inlineStr"/>
+      <c r="BA36" s="2" t="inlineStr"/>
+      <c r="BB36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -9163,6 +9368,11 @@
       </c>
       <c r="AV37" s="4" t="inlineStr"/>
       <c r="AW37" s="4" t="inlineStr"/>
+      <c r="AX37" s="4" t="inlineStr"/>
+      <c r="AY37" s="4" t="inlineStr"/>
+      <c r="AZ37" s="4" t="inlineStr"/>
+      <c r="BA37" s="4" t="inlineStr"/>
+      <c r="BB37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -9399,6 +9609,11 @@
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" s="2" t="inlineStr"/>
+      <c r="AX38" s="2" t="inlineStr"/>
+      <c r="AY38" s="2" t="inlineStr"/>
+      <c r="AZ38" s="2" t="inlineStr"/>
+      <c r="BA38" s="2" t="inlineStr"/>
+      <c r="BB38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -9634,6 +9849,11 @@
       </c>
       <c r="AV39" s="4" t="inlineStr"/>
       <c r="AW39" s="4" t="inlineStr"/>
+      <c r="AX39" s="4" t="inlineStr"/>
+      <c r="AY39" s="4" t="inlineStr"/>
+      <c r="AZ39" s="4" t="inlineStr"/>
+      <c r="BA39" s="4" t="inlineStr"/>
+      <c r="BB39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -9869,6 +10089,11 @@
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" s="2" t="inlineStr"/>
+      <c r="AX40" s="2" t="inlineStr"/>
+      <c r="AY40" s="2" t="inlineStr"/>
+      <c r="AZ40" s="2" t="inlineStr"/>
+      <c r="BA40" s="2" t="inlineStr"/>
+      <c r="BB40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -10105,6 +10330,11 @@
       </c>
       <c r="AV41" s="4" t="inlineStr"/>
       <c r="AW41" s="4" t="inlineStr"/>
+      <c r="AX41" s="4" t="inlineStr"/>
+      <c r="AY41" s="4" t="inlineStr"/>
+      <c r="AZ41" s="4" t="inlineStr"/>
+      <c r="BA41" s="4" t="inlineStr"/>
+      <c r="BB41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -10344,6 +10574,11 @@
           <t>https://web.microsoftstream.com/video/1689d147-ff5e-41df-9e77-e9270bae338b?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX42" s="2" t="inlineStr"/>
+      <c r="AY42" s="2" t="inlineStr"/>
+      <c r="AZ42" s="2" t="inlineStr"/>
+      <c r="BA42" s="2" t="inlineStr"/>
+      <c r="BB42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -10580,6 +10815,11 @@
       </c>
       <c r="AV43" s="4" t="inlineStr"/>
       <c r="AW43" s="4" t="inlineStr"/>
+      <c r="AX43" s="4" t="inlineStr"/>
+      <c r="AY43" s="4" t="inlineStr"/>
+      <c r="AZ43" s="4" t="inlineStr"/>
+      <c r="BA43" s="4" t="inlineStr"/>
+      <c r="BB43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -10807,6 +11047,11 @@
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" s="2" t="inlineStr"/>
+      <c r="AX44" s="2" t="inlineStr"/>
+      <c r="AY44" s="2" t="inlineStr"/>
+      <c r="AZ44" s="2" t="inlineStr"/>
+      <c r="BA44" s="2" t="inlineStr"/>
+      <c r="BB44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -11046,6 +11291,11 @@
           <t>https://web.microsoftstream.com/video/f0b7478a-7800-4df0-8a43-0113c5248eec?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX45" s="4" t="inlineStr"/>
+      <c r="AY45" s="4" t="inlineStr"/>
+      <c r="AZ45" s="4" t="inlineStr"/>
+      <c r="BA45" s="4" t="inlineStr"/>
+      <c r="BB45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -11281,6 +11531,11 @@
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" s="2" t="inlineStr"/>
+      <c r="AX46" s="2" t="inlineStr"/>
+      <c r="AY46" s="2" t="inlineStr"/>
+      <c r="AZ46" s="2" t="inlineStr"/>
+      <c r="BA46" s="2" t="inlineStr"/>
+      <c r="BB46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -11520,6 +11775,11 @@
           <t>https://web.microsoftstream.com/video/5f6afa60-a43f-403c-8879-e04a2d36c5fa?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX47" s="4" t="inlineStr"/>
+      <c r="AY47" s="4" t="inlineStr"/>
+      <c r="AZ47" s="4" t="inlineStr"/>
+      <c r="BA47" s="4" t="inlineStr"/>
+      <c r="BB47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -11755,6 +12015,11 @@
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" s="2" t="inlineStr"/>
+      <c r="AX48" s="2" t="inlineStr"/>
+      <c r="AY48" s="2" t="inlineStr"/>
+      <c r="AZ48" s="2" t="inlineStr"/>
+      <c r="BA48" s="2" t="inlineStr"/>
+      <c r="BB48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -11995,6 +12260,11 @@
           <t>https://web.microsoftstream.com/video/ee622bf6-774a-41bd-afd8-1775b6b730b9?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX49" s="4" t="inlineStr"/>
+      <c r="AY49" s="4" t="inlineStr"/>
+      <c r="AZ49" s="4" t="inlineStr"/>
+      <c r="BA49" s="4" t="inlineStr"/>
+      <c r="BB49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -12230,6 +12500,11 @@
           <t>https://web.microsoftstream.com/video/4be15710-4acb-4afd-a959-c6ed0d090cac?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX50" s="2" t="inlineStr"/>
+      <c r="AY50" s="2" t="inlineStr"/>
+      <c r="AZ50" s="2" t="inlineStr"/>
+      <c r="BA50" s="2" t="inlineStr"/>
+      <c r="BB50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -12469,6 +12744,11 @@
           <t>https://web.microsoftstream.com/video/3cd97374-bb4b-4204-bdef-48cfa0e370c8?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX51" s="4" t="inlineStr"/>
+      <c r="AY51" s="4" t="inlineStr"/>
+      <c r="AZ51" s="4" t="inlineStr"/>
+      <c r="BA51" s="4" t="inlineStr"/>
+      <c r="BB51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -12704,6 +12984,11 @@
           <t>https://web.microsoftstream.com/video/6fd51e32-7197-4736-ab0d-031b75c372fd?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX52" s="2" t="inlineStr"/>
+      <c r="AY52" s="2" t="inlineStr"/>
+      <c r="AZ52" s="2" t="inlineStr"/>
+      <c r="BA52" s="2" t="inlineStr"/>
+      <c r="BB52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -12939,6 +13224,11 @@
           <t>https://web.microsoftstream.com/video/5f0c9eff-f752-448b-8f0a-3e2fff710aa9?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX53" s="4" t="inlineStr"/>
+      <c r="AY53" s="4" t="inlineStr"/>
+      <c r="AZ53" s="4" t="inlineStr"/>
+      <c r="BA53" s="4" t="inlineStr"/>
+      <c r="BB53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -13174,6 +13464,11 @@
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" s="2" t="inlineStr"/>
+      <c r="AX54" s="2" t="inlineStr"/>
+      <c r="AY54" s="2" t="inlineStr"/>
+      <c r="AZ54" s="2" t="inlineStr"/>
+      <c r="BA54" s="2" t="inlineStr"/>
+      <c r="BB54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -13401,6 +13696,11 @@
       </c>
       <c r="AV55" s="4" t="inlineStr"/>
       <c r="AW55" s="4" t="inlineStr"/>
+      <c r="AX55" s="4" t="inlineStr"/>
+      <c r="AY55" s="4" t="inlineStr"/>
+      <c r="AZ55" s="4" t="inlineStr"/>
+      <c r="BA55" s="4" t="inlineStr"/>
+      <c r="BB55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -13646,6 +13946,11 @@
           <t>https://web.microsoftstream.com/video/ca76c442-41bd-4e49-bf93-7c88dfc75f01?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX56" s="2" t="inlineStr"/>
+      <c r="AY56" s="2" t="inlineStr"/>
+      <c r="AZ56" s="2" t="inlineStr"/>
+      <c r="BA56" s="2" t="inlineStr"/>
+      <c r="BB56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -13885,6 +14190,11 @@
           <t>https://web.microsoftstream.com/video/86aa0100-d5af-4db2-9f67-441255924e4e?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX57" s="4" t="inlineStr"/>
+      <c r="AY57" s="4" t="inlineStr"/>
+      <c r="AZ57" s="4" t="inlineStr"/>
+      <c r="BA57" s="4" t="inlineStr"/>
+      <c r="BB57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -14116,6 +14426,11 @@
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" s="2" t="inlineStr"/>
+      <c r="AX58" s="2" t="inlineStr"/>
+      <c r="AY58" s="2" t="inlineStr"/>
+      <c r="AZ58" s="2" t="inlineStr"/>
+      <c r="BA58" s="2" t="inlineStr"/>
+      <c r="BB58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -14347,6 +14662,11 @@
       </c>
       <c r="AV59" s="4" t="inlineStr"/>
       <c r="AW59" s="4" t="inlineStr"/>
+      <c r="AX59" s="4" t="inlineStr"/>
+      <c r="AY59" s="4" t="inlineStr"/>
+      <c r="AZ59" s="4" t="inlineStr"/>
+      <c r="BA59" s="4" t="inlineStr"/>
+      <c r="BB59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -14574,6 +14894,11 @@
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" s="2" t="inlineStr"/>
+      <c r="AX60" s="2" t="inlineStr"/>
+      <c r="AY60" s="2" t="inlineStr"/>
+      <c r="AZ60" s="2" t="inlineStr"/>
+      <c r="BA60" s="2" t="inlineStr"/>
+      <c r="BB60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -14805,6 +15130,11 @@
       </c>
       <c r="AV61" s="4" t="inlineStr"/>
       <c r="AW61" s="4" t="inlineStr"/>
+      <c r="AX61" s="4" t="inlineStr"/>
+      <c r="AY61" s="4" t="inlineStr"/>
+      <c r="AZ61" s="4" t="inlineStr"/>
+      <c r="BA61" s="4" t="inlineStr"/>
+      <c r="BB61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -15036,6 +15366,11 @@
       </c>
       <c r="AV62" s="2" t="inlineStr"/>
       <c r="AW62" s="2" t="inlineStr"/>
+      <c r="AX62" s="2" t="inlineStr"/>
+      <c r="AY62" s="2" t="inlineStr"/>
+      <c r="AZ62" s="2" t="inlineStr"/>
+      <c r="BA62" s="2" t="inlineStr"/>
+      <c r="BB62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -15263,6 +15598,11 @@
       </c>
       <c r="AV63" s="4" t="inlineStr"/>
       <c r="AW63" s="4" t="inlineStr"/>
+      <c r="AX63" s="4" t="inlineStr"/>
+      <c r="AY63" s="4" t="inlineStr"/>
+      <c r="AZ63" s="4" t="inlineStr"/>
+      <c r="BA63" s="4" t="inlineStr"/>
+      <c r="BB63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -15494,6 +15834,11 @@
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" s="2" t="inlineStr"/>
+      <c r="AX64" s="2" t="inlineStr"/>
+      <c r="AY64" s="2" t="inlineStr"/>
+      <c r="AZ64" s="2" t="inlineStr"/>
+      <c r="BA64" s="2" t="inlineStr"/>
+      <c r="BB64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -15721,6 +16066,11 @@
       </c>
       <c r="AV65" s="4" t="inlineStr"/>
       <c r="AW65" s="4" t="inlineStr"/>
+      <c r="AX65" s="4" t="inlineStr"/>
+      <c r="AY65" s="4" t="inlineStr"/>
+      <c r="AZ65" s="4" t="inlineStr"/>
+      <c r="BA65" s="4" t="inlineStr"/>
+      <c r="BB65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -15952,6 +16302,11 @@
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" s="2" t="inlineStr"/>
+      <c r="AX66" s="2" t="inlineStr"/>
+      <c r="AY66" s="2" t="inlineStr"/>
+      <c r="AZ66" s="2" t="inlineStr"/>
+      <c r="BA66" s="2" t="inlineStr"/>
+      <c r="BB66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -16187,6 +16542,11 @@
       </c>
       <c r="AV67" s="4" t="inlineStr"/>
       <c r="AW67" s="4" t="inlineStr"/>
+      <c r="AX67" s="4" t="inlineStr"/>
+      <c r="AY67" s="4" t="inlineStr"/>
+      <c r="AZ67" s="4" t="inlineStr"/>
+      <c r="BA67" s="4" t="inlineStr"/>
+      <c r="BB67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -16422,6 +16782,11 @@
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" s="2" t="inlineStr"/>
+      <c r="AX68" s="2" t="inlineStr"/>
+      <c r="AY68" s="2" t="inlineStr"/>
+      <c r="AZ68" s="2" t="inlineStr"/>
+      <c r="BA68" s="2" t="inlineStr"/>
+      <c r="BB68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -16653,6 +17018,11 @@
       </c>
       <c r="AV69" s="4" t="inlineStr"/>
       <c r="AW69" s="4" t="inlineStr"/>
+      <c r="AX69" s="4" t="inlineStr"/>
+      <c r="AY69" s="4" t="inlineStr"/>
+      <c r="AZ69" s="4" t="inlineStr"/>
+      <c r="BA69" s="4" t="inlineStr"/>
+      <c r="BB69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -16888,6 +17258,11 @@
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" s="2" t="inlineStr"/>
+      <c r="AX70" s="2" t="inlineStr"/>
+      <c r="AY70" s="2" t="inlineStr"/>
+      <c r="AZ70" s="2" t="inlineStr"/>
+      <c r="BA70" s="2" t="inlineStr"/>
+      <c r="BB70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -17123,6 +17498,11 @@
           <t>https://web.microsoftstream.com/video/7ad96d1d-faee-497b-9eb5-c3093ebf417d?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX71" s="4" t="inlineStr"/>
+      <c r="AY71" s="4" t="inlineStr"/>
+      <c r="AZ71" s="4" t="inlineStr"/>
+      <c r="BA71" s="4" t="inlineStr"/>
+      <c r="BB71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -17358,6 +17738,11 @@
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" s="2" t="inlineStr"/>
+      <c r="AX72" s="2" t="inlineStr"/>
+      <c r="AY72" s="2" t="inlineStr"/>
+      <c r="AZ72" s="2" t="inlineStr"/>
+      <c r="BA72" s="2" t="inlineStr"/>
+      <c r="BB72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -17581,6 +17966,11 @@
       </c>
       <c r="AV73" s="4" t="inlineStr"/>
       <c r="AW73" s="4" t="inlineStr"/>
+      <c r="AX73" s="4" t="inlineStr"/>
+      <c r="AY73" s="4" t="inlineStr"/>
+      <c r="AZ73" s="4" t="inlineStr"/>
+      <c r="BA73" s="4" t="inlineStr"/>
+      <c r="BB73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -17823,6 +18213,11 @@
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" s="2" t="inlineStr"/>
+      <c r="AX74" s="2" t="inlineStr"/>
+      <c r="AY74" s="2" t="inlineStr"/>
+      <c r="AZ74" s="2" t="inlineStr"/>
+      <c r="BA74" s="2" t="inlineStr"/>
+      <c r="BB74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -18064,6 +18459,11 @@
       </c>
       <c r="AV75" s="4" t="inlineStr"/>
       <c r="AW75" s="4" t="inlineStr"/>
+      <c r="AX75" s="4" t="inlineStr"/>
+      <c r="AY75" s="4" t="inlineStr"/>
+      <c r="AZ75" s="4" t="inlineStr"/>
+      <c r="BA75" s="4" t="inlineStr"/>
+      <c r="BB75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -18305,6 +18705,11 @@
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" s="2" t="inlineStr"/>
+      <c r="AX76" s="2" t="inlineStr"/>
+      <c r="AY76" s="2" t="inlineStr"/>
+      <c r="AZ76" s="2" t="inlineStr"/>
+      <c r="BA76" s="2" t="inlineStr"/>
+      <c r="BB76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -18548,6 +18953,11 @@
       </c>
       <c r="AV77" s="4" t="inlineStr"/>
       <c r="AW77" s="4" t="inlineStr"/>
+      <c r="AX77" s="4" t="inlineStr"/>
+      <c r="AY77" s="4" t="inlineStr"/>
+      <c r="AZ77" s="4" t="inlineStr"/>
+      <c r="BA77" s="4" t="inlineStr"/>
+      <c r="BB77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -18602,7 +19012,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-capital-protegido-ciclico-ii-multimercado-lp/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fim-cap-protegido-ciclico-ii</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -18791,6 +19201,11 @@
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" s="2" t="inlineStr"/>
+      <c r="AX78" s="2" t="inlineStr"/>
+      <c r="AY78" s="2" t="inlineStr"/>
+      <c r="AZ78" s="2" t="inlineStr"/>
+      <c r="BA78" s="2" t="inlineStr"/>
+      <c r="BB78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -19022,6 +19437,11 @@
       </c>
       <c r="AV79" s="4" t="inlineStr"/>
       <c r="AW79" s="4" t="inlineStr"/>
+      <c r="AX79" s="4" t="inlineStr"/>
+      <c r="AY79" s="4" t="inlineStr"/>
+      <c r="AZ79" s="4" t="inlineStr"/>
+      <c r="BA79" s="4" t="inlineStr"/>
+      <c r="BB79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -19257,6 +19677,11 @@
           <t>https://web.microsoftstream.com/video/2cbfedbd-9ece-40fb-9cc2-7d866c3c427e?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX80" s="2" t="inlineStr"/>
+      <c r="AY80" s="2" t="inlineStr"/>
+      <c r="AZ80" s="2" t="inlineStr"/>
+      <c r="BA80" s="2" t="inlineStr"/>
+      <c r="BB80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -19488,6 +19913,11 @@
       </c>
       <c r="AV81" s="4" t="inlineStr"/>
       <c r="AW81" s="4" t="inlineStr"/>
+      <c r="AX81" s="4" t="inlineStr"/>
+      <c r="AY81" s="4" t="inlineStr"/>
+      <c r="AZ81" s="4" t="inlineStr"/>
+      <c r="BA81" s="4" t="inlineStr"/>
+      <c r="BB81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -19719,6 +20149,11 @@
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" s="2" t="inlineStr"/>
+      <c r="AX82" s="2" t="inlineStr"/>
+      <c r="AY82" s="2" t="inlineStr"/>
+      <c r="AZ82" s="2" t="inlineStr"/>
+      <c r="BA82" s="2" t="inlineStr"/>
+      <c r="BB82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -19955,6 +20390,11 @@
       </c>
       <c r="AV83" s="4" t="inlineStr"/>
       <c r="AW83" s="4" t="inlineStr"/>
+      <c r="AX83" s="4" t="inlineStr"/>
+      <c r="AY83" s="4" t="inlineStr"/>
+      <c r="AZ83" s="4" t="inlineStr"/>
+      <c r="BA83" s="4" t="inlineStr"/>
+      <c r="BB83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -20190,6 +20630,11 @@
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" s="2" t="inlineStr"/>
+      <c r="AX84" s="2" t="inlineStr"/>
+      <c r="AY84" s="2" t="inlineStr"/>
+      <c r="AZ84" s="2" t="inlineStr"/>
+      <c r="BA84" s="2" t="inlineStr"/>
+      <c r="BB84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -20425,6 +20870,11 @@
       </c>
       <c r="AV85" s="4" t="inlineStr"/>
       <c r="AW85" s="4" t="inlineStr"/>
+      <c r="AX85" s="4" t="inlineStr"/>
+      <c r="AY85" s="4" t="inlineStr"/>
+      <c r="AZ85" s="4" t="inlineStr"/>
+      <c r="BA85" s="4" t="inlineStr"/>
+      <c r="BB85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -20660,6 +21110,11 @@
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" s="2" t="inlineStr"/>
+      <c r="AX86" s="2" t="inlineStr"/>
+      <c r="AY86" s="2" t="inlineStr"/>
+      <c r="AZ86" s="2" t="inlineStr"/>
+      <c r="BA86" s="2" t="inlineStr"/>
+      <c r="BB86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -20895,6 +21350,11 @@
       </c>
       <c r="AV87" s="4" t="inlineStr"/>
       <c r="AW87" s="4" t="inlineStr"/>
+      <c r="AX87" s="4" t="inlineStr"/>
+      <c r="AY87" s="4" t="inlineStr"/>
+      <c r="AZ87" s="4" t="inlineStr"/>
+      <c r="BA87" s="4" t="inlineStr"/>
+      <c r="BB87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -21119,6 +21579,11 @@
       </c>
       <c r="AV88" s="2" t="inlineStr"/>
       <c r="AW88" s="2" t="inlineStr"/>
+      <c r="AX88" s="2" t="inlineStr"/>
+      <c r="AY88" s="2" t="inlineStr"/>
+      <c r="AZ88" s="2" t="inlineStr"/>
+      <c r="BA88" s="2" t="inlineStr"/>
+      <c r="BB88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -21354,6 +21819,11 @@
       </c>
       <c r="AV89" s="4" t="inlineStr"/>
       <c r="AW89" s="4" t="inlineStr"/>
+      <c r="AX89" s="4" t="inlineStr"/>
+      <c r="AY89" s="4" t="inlineStr"/>
+      <c r="AZ89" s="4" t="inlineStr"/>
+      <c r="BA89" s="4" t="inlineStr"/>
+      <c r="BB89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -21589,6 +22059,11 @@
       </c>
       <c r="AV90" s="2" t="inlineStr"/>
       <c r="AW90" s="2" t="inlineStr"/>
+      <c r="AX90" s="2" t="inlineStr"/>
+      <c r="AY90" s="2" t="inlineStr"/>
+      <c r="AZ90" s="2" t="inlineStr"/>
+      <c r="BA90" s="2" t="inlineStr"/>
+      <c r="BB90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -21824,6 +22299,11 @@
       </c>
       <c r="AV91" s="4" t="inlineStr"/>
       <c r="AW91" s="4" t="inlineStr"/>
+      <c r="AX91" s="4" t="inlineStr"/>
+      <c r="AY91" s="4" t="inlineStr"/>
+      <c r="AZ91" s="4" t="inlineStr"/>
+      <c r="BA91" s="4" t="inlineStr"/>
+      <c r="BB91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -22059,6 +22539,11 @@
       </c>
       <c r="AV92" s="2" t="inlineStr"/>
       <c r="AW92" s="2" t="inlineStr"/>
+      <c r="AX92" s="2" t="inlineStr"/>
+      <c r="AY92" s="2" t="inlineStr"/>
+      <c r="AZ92" s="2" t="inlineStr"/>
+      <c r="BA92" s="2" t="inlineStr"/>
+      <c r="BB92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -22294,6 +22779,11 @@
       </c>
       <c r="AV93" s="4" t="inlineStr"/>
       <c r="AW93" s="4" t="inlineStr"/>
+      <c r="AX93" s="4" t="inlineStr"/>
+      <c r="AY93" s="4" t="inlineStr"/>
+      <c r="AZ93" s="4" t="inlineStr"/>
+      <c r="BA93" s="4" t="inlineStr"/>
+      <c r="BB93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -22529,6 +23019,11 @@
       </c>
       <c r="AV94" s="2" t="inlineStr"/>
       <c r="AW94" s="2" t="inlineStr"/>
+      <c r="AX94" s="2" t="inlineStr"/>
+      <c r="AY94" s="2" t="inlineStr"/>
+      <c r="AZ94" s="2" t="inlineStr"/>
+      <c r="BA94" s="2" t="inlineStr"/>
+      <c r="BB94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -22764,6 +23259,11 @@
       </c>
       <c r="AV95" s="4" t="inlineStr"/>
       <c r="AW95" s="4" t="inlineStr"/>
+      <c r="AX95" s="4" t="inlineStr"/>
+      <c r="AY95" s="4" t="inlineStr"/>
+      <c r="AZ95" s="4" t="inlineStr"/>
+      <c r="BA95" s="4" t="inlineStr"/>
+      <c r="BB95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -22999,6 +23499,11 @@
       </c>
       <c r="AV96" s="2" t="inlineStr"/>
       <c r="AW96" s="2" t="inlineStr"/>
+      <c r="AX96" s="2" t="inlineStr"/>
+      <c r="AY96" s="2" t="inlineStr"/>
+      <c r="AZ96" s="2" t="inlineStr"/>
+      <c r="BA96" s="2" t="inlineStr"/>
+      <c r="BB96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -23234,6 +23739,11 @@
       </c>
       <c r="AV97" s="4" t="inlineStr"/>
       <c r="AW97" s="4" t="inlineStr"/>
+      <c r="AX97" s="4" t="inlineStr"/>
+      <c r="AY97" s="4" t="inlineStr"/>
+      <c r="AZ97" s="4" t="inlineStr"/>
+      <c r="BA97" s="4" t="inlineStr"/>
+      <c r="BB97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -23473,6 +23983,11 @@
           <t>https://web.microsoftstream.com/video/c97500d6-f87e-4c24-a7f6-50fa0a703f14?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX98" s="2" t="inlineStr"/>
+      <c r="AY98" s="2" t="inlineStr"/>
+      <c r="AZ98" s="2" t="inlineStr"/>
+      <c r="BA98" s="2" t="inlineStr"/>
+      <c r="BB98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -23708,6 +24223,11 @@
       </c>
       <c r="AV99" s="4" t="inlineStr"/>
       <c r="AW99" s="4" t="inlineStr"/>
+      <c r="AX99" s="4" t="inlineStr"/>
+      <c r="AY99" s="4" t="inlineStr"/>
+      <c r="AZ99" s="4" t="inlineStr"/>
+      <c r="BA99" s="4" t="inlineStr"/>
+      <c r="BB99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -23943,6 +24463,11 @@
       </c>
       <c r="AV100" s="2" t="inlineStr"/>
       <c r="AW100" s="2" t="inlineStr"/>
+      <c r="AX100" s="2" t="inlineStr"/>
+      <c r="AY100" s="2" t="inlineStr"/>
+      <c r="AZ100" s="2" t="inlineStr"/>
+      <c r="BA100" s="2" t="inlineStr"/>
+      <c r="BB100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -24178,6 +24703,11 @@
       </c>
       <c r="AV101" s="4" t="inlineStr"/>
       <c r="AW101" s="4" t="inlineStr"/>
+      <c r="AX101" s="4" t="inlineStr"/>
+      <c r="AY101" s="4" t="inlineStr"/>
+      <c r="AZ101" s="4" t="inlineStr"/>
+      <c r="BA101" s="4" t="inlineStr"/>
+      <c r="BB101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -24417,6 +24947,11 @@
       </c>
       <c r="AV102" s="2" t="inlineStr"/>
       <c r="AW102" s="2" t="inlineStr"/>
+      <c r="AX102" s="2" t="inlineStr"/>
+      <c r="AY102" s="2" t="inlineStr"/>
+      <c r="AZ102" s="2" t="inlineStr"/>
+      <c r="BA102" s="2" t="inlineStr"/>
+      <c r="BB102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -24652,6 +25187,11 @@
       </c>
       <c r="AV103" s="4" t="inlineStr"/>
       <c r="AW103" s="4" t="inlineStr"/>
+      <c r="AX103" s="4" t="inlineStr"/>
+      <c r="AY103" s="4" t="inlineStr"/>
+      <c r="AZ103" s="4" t="inlineStr"/>
+      <c r="BA103" s="4" t="inlineStr"/>
+      <c r="BB103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -24887,6 +25427,11 @@
       </c>
       <c r="AV104" s="2" t="inlineStr"/>
       <c r="AW104" s="2" t="inlineStr"/>
+      <c r="AX104" s="2" t="inlineStr"/>
+      <c r="AY104" s="2" t="inlineStr"/>
+      <c r="AZ104" s="2" t="inlineStr"/>
+      <c r="BA104" s="2" t="inlineStr"/>
+      <c r="BB104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -25114,6 +25659,11 @@
       </c>
       <c r="AV105" s="4" t="inlineStr"/>
       <c r="AW105" s="4" t="inlineStr"/>
+      <c r="AX105" s="4" t="inlineStr"/>
+      <c r="AY105" s="4" t="inlineStr"/>
+      <c r="AZ105" s="4" t="inlineStr"/>
+      <c r="BA105" s="4" t="inlineStr"/>
+      <c r="BB105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -25341,6 +25891,11 @@
       </c>
       <c r="AV106" s="2" t="inlineStr"/>
       <c r="AW106" s="2" t="inlineStr"/>
+      <c r="AX106" s="2" t="inlineStr"/>
+      <c r="AY106" s="2" t="inlineStr"/>
+      <c r="AZ106" s="2" t="inlineStr"/>
+      <c r="BA106" s="2" t="inlineStr"/>
+      <c r="BB106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -25576,6 +26131,11 @@
       </c>
       <c r="AV107" s="4" t="inlineStr"/>
       <c r="AW107" s="4" t="inlineStr"/>
+      <c r="AX107" s="4" t="inlineStr"/>
+      <c r="AY107" s="4" t="inlineStr"/>
+      <c r="AZ107" s="4" t="inlineStr"/>
+      <c r="BA107" s="4" t="inlineStr"/>
+      <c r="BB107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -25811,6 +26371,11 @@
       </c>
       <c r="AV108" s="2" t="inlineStr"/>
       <c r="AW108" s="2" t="inlineStr"/>
+      <c r="AX108" s="2" t="inlineStr"/>
+      <c r="AY108" s="2" t="inlineStr"/>
+      <c r="AZ108" s="2" t="inlineStr"/>
+      <c r="BA108" s="2" t="inlineStr"/>
+      <c r="BB108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -26042,6 +26607,11 @@
       </c>
       <c r="AV109" s="4" t="inlineStr"/>
       <c r="AW109" s="4" t="inlineStr"/>
+      <c r="AX109" s="4" t="inlineStr"/>
+      <c r="AY109" s="4" t="inlineStr"/>
+      <c r="AZ109" s="4" t="inlineStr"/>
+      <c r="BA109" s="4" t="inlineStr"/>
+      <c r="BB109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -26273,6 +26843,11 @@
       </c>
       <c r="AV110" s="2" t="inlineStr"/>
       <c r="AW110" s="2" t="inlineStr"/>
+      <c r="AX110" s="2" t="inlineStr"/>
+      <c r="AY110" s="2" t="inlineStr"/>
+      <c r="AZ110" s="2" t="inlineStr"/>
+      <c r="BA110" s="2" t="inlineStr"/>
+      <c r="BB110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -26508,6 +27083,11 @@
       </c>
       <c r="AV111" s="4" t="inlineStr"/>
       <c r="AW111" s="4" t="inlineStr"/>
+      <c r="AX111" s="4" t="inlineStr"/>
+      <c r="AY111" s="4" t="inlineStr"/>
+      <c r="AZ111" s="4" t="inlineStr"/>
+      <c r="BA111" s="4" t="inlineStr"/>
+      <c r="BB111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -26747,6 +27327,11 @@
       </c>
       <c r="AV112" s="2" t="inlineStr"/>
       <c r="AW112" s="2" t="inlineStr"/>
+      <c r="AX112" s="2" t="inlineStr"/>
+      <c r="AY112" s="2" t="inlineStr"/>
+      <c r="AZ112" s="2" t="inlineStr"/>
+      <c r="BA112" s="2" t="inlineStr"/>
+      <c r="BB112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -26982,6 +27567,11 @@
       </c>
       <c r="AV113" s="4" t="inlineStr"/>
       <c r="AW113" s="4" t="inlineStr"/>
+      <c r="AX113" s="4" t="inlineStr"/>
+      <c r="AY113" s="4" t="inlineStr"/>
+      <c r="AZ113" s="4" t="inlineStr"/>
+      <c r="BA113" s="4" t="inlineStr"/>
+      <c r="BB113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -27213,6 +27803,11 @@
       </c>
       <c r="AV114" s="2" t="inlineStr"/>
       <c r="AW114" s="2" t="inlineStr"/>
+      <c r="AX114" s="2" t="inlineStr"/>
+      <c r="AY114" s="2" t="inlineStr"/>
+      <c r="AZ114" s="2" t="inlineStr"/>
+      <c r="BA114" s="2" t="inlineStr"/>
+      <c r="BB114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -27448,6 +28043,11 @@
       </c>
       <c r="AV115" s="4" t="inlineStr"/>
       <c r="AW115" s="4" t="inlineStr"/>
+      <c r="AX115" s="4" t="inlineStr"/>
+      <c r="AY115" s="4" t="inlineStr"/>
+      <c r="AZ115" s="4" t="inlineStr"/>
+      <c r="BA115" s="4" t="inlineStr"/>
+      <c r="BB115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -27680,6 +28280,11 @@
       </c>
       <c r="AV116" s="2" t="inlineStr"/>
       <c r="AW116" s="2" t="inlineStr"/>
+      <c r="AX116" s="2" t="inlineStr"/>
+      <c r="AY116" s="2" t="inlineStr"/>
+      <c r="AZ116" s="2" t="inlineStr"/>
+      <c r="BA116" s="2" t="inlineStr"/>
+      <c r="BB116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -27908,6 +28513,11 @@
       </c>
       <c r="AV117" s="4" t="inlineStr"/>
       <c r="AW117" s="4" t="inlineStr"/>
+      <c r="AX117" s="4" t="inlineStr"/>
+      <c r="AY117" s="4" t="inlineStr"/>
+      <c r="AZ117" s="4" t="inlineStr"/>
+      <c r="BA117" s="4" t="inlineStr"/>
+      <c r="BB117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -28127,6 +28737,11 @@
       </c>
       <c r="AV118" s="2" t="inlineStr"/>
       <c r="AW118" s="2" t="inlineStr"/>
+      <c r="AX118" s="2" t="inlineStr"/>
+      <c r="AY118" s="2" t="inlineStr"/>
+      <c r="AZ118" s="2" t="inlineStr"/>
+      <c r="BA118" s="2" t="inlineStr"/>
+      <c r="BB118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -28346,6 +28961,11 @@
       </c>
       <c r="AV119" s="4" t="inlineStr"/>
       <c r="AW119" s="4" t="inlineStr"/>
+      <c r="AX119" s="4" t="inlineStr"/>
+      <c r="AY119" s="4" t="inlineStr"/>
+      <c r="AZ119" s="4" t="inlineStr"/>
+      <c r="BA119" s="4" t="inlineStr"/>
+      <c r="BB119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -28574,6 +29194,11 @@
           <t>https://web.microsoftstream.com/video/462482fb-026d-4ac5-8d29-95b943fd4e67?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX120" s="2" t="inlineStr"/>
+      <c r="AY120" s="2" t="inlineStr"/>
+      <c r="AZ120" s="2" t="inlineStr"/>
+      <c r="BA120" s="2" t="inlineStr"/>
+      <c r="BB120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -28798,6 +29423,11 @@
       </c>
       <c r="AV121" s="4" t="inlineStr"/>
       <c r="AW121" s="4" t="inlineStr"/>
+      <c r="AX121" s="4" t="inlineStr"/>
+      <c r="AY121" s="4" t="inlineStr"/>
+      <c r="AZ121" s="4" t="inlineStr"/>
+      <c r="BA121" s="4" t="inlineStr"/>
+      <c r="BB121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -29022,6 +29652,11 @@
       </c>
       <c r="AV122" s="2" t="inlineStr"/>
       <c r="AW122" s="2" t="inlineStr"/>
+      <c r="AX122" s="2" t="inlineStr"/>
+      <c r="AY122" s="2" t="inlineStr"/>
+      <c r="AZ122" s="2" t="inlineStr"/>
+      <c r="BA122" s="2" t="inlineStr"/>
+      <c r="BB122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -29241,6 +29876,11 @@
       </c>
       <c r="AV123" s="4" t="inlineStr"/>
       <c r="AW123" s="4" t="inlineStr"/>
+      <c r="AX123" s="4" t="inlineStr"/>
+      <c r="AY123" s="4" t="inlineStr"/>
+      <c r="AZ123" s="4" t="inlineStr"/>
+      <c r="BA123" s="4" t="inlineStr"/>
+      <c r="BB123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -29464,6 +30104,11 @@
       </c>
       <c r="AV124" s="2" t="inlineStr"/>
       <c r="AW124" s="2" t="inlineStr"/>
+      <c r="AX124" s="2" t="inlineStr"/>
+      <c r="AY124" s="2" t="inlineStr"/>
+      <c r="AZ124" s="2" t="inlineStr"/>
+      <c r="BA124" s="2" t="inlineStr"/>
+      <c r="BB124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -29700,6 +30345,11 @@
       </c>
       <c r="AV125" s="4" t="inlineStr"/>
       <c r="AW125" s="4" t="inlineStr"/>
+      <c r="AX125" s="4" t="inlineStr"/>
+      <c r="AY125" s="4" t="inlineStr"/>
+      <c r="AZ125" s="4" t="inlineStr"/>
+      <c r="BA125" s="4" t="inlineStr"/>
+      <c r="BB125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -29940,6 +30590,11 @@
       </c>
       <c r="AV126" s="2" t="inlineStr"/>
       <c r="AW126" s="2" t="inlineStr"/>
+      <c r="AX126" s="2" t="inlineStr"/>
+      <c r="AY126" s="2" t="inlineStr"/>
+      <c r="AZ126" s="2" t="inlineStr"/>
+      <c r="BA126" s="2" t="inlineStr"/>
+      <c r="BB126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -30176,6 +30831,11 @@
       </c>
       <c r="AV127" s="4" t="inlineStr"/>
       <c r="AW127" s="4" t="inlineStr"/>
+      <c r="AX127" s="4" t="inlineStr"/>
+      <c r="AY127" s="4" t="inlineStr"/>
+      <c r="AZ127" s="4" t="inlineStr"/>
+      <c r="BA127" s="4" t="inlineStr"/>
+      <c r="BB127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -30408,6 +31068,11 @@
       </c>
       <c r="AV128" s="2" t="inlineStr"/>
       <c r="AW128" s="2" t="inlineStr"/>
+      <c r="AX128" s="2" t="inlineStr"/>
+      <c r="AY128" s="2" t="inlineStr"/>
+      <c r="AZ128" s="2" t="inlineStr"/>
+      <c r="BA128" s="2" t="inlineStr"/>
+      <c r="BB128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -30645,6 +31310,11 @@
       </c>
       <c r="AV129" s="4" t="inlineStr"/>
       <c r="AW129" s="4" t="inlineStr"/>
+      <c r="AX129" s="4" t="inlineStr"/>
+      <c r="AY129" s="4" t="inlineStr"/>
+      <c r="AZ129" s="4" t="inlineStr"/>
+      <c r="BA129" s="4" t="inlineStr"/>
+      <c r="BB129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -30884,6 +31554,11 @@
           <t>https://web.microsoftstream.com/video/140b7682-00df-491d-b451-73ae70a040fa?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX130" s="2" t="inlineStr"/>
+      <c r="AY130" s="2" t="inlineStr"/>
+      <c r="AZ130" s="2" t="inlineStr"/>
+      <c r="BA130" s="2" t="inlineStr"/>
+      <c r="BB130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -31120,6 +31795,11 @@
       </c>
       <c r="AV131" s="4" t="inlineStr"/>
       <c r="AW131" s="4" t="inlineStr"/>
+      <c r="AX131" s="4" t="inlineStr"/>
+      <c r="AY131" s="4" t="inlineStr"/>
+      <c r="AZ131" s="4" t="inlineStr"/>
+      <c r="BA131" s="4" t="inlineStr"/>
+      <c r="BB131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -31355,6 +32035,11 @@
           <t>https://web.microsoftstream.com/video/513ae285-b3cb-42e6-a51a-984face9af08?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX132" s="2" t="inlineStr"/>
+      <c r="AY132" s="2" t="inlineStr"/>
+      <c r="AZ132" s="2" t="inlineStr"/>
+      <c r="BA132" s="2" t="inlineStr"/>
+      <c r="BB132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -31590,6 +32275,11 @@
           <t>https://web.microsoftstream.com/video/edcf6e85-7c1c-4dd4-9cc1-599dd69841dc?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX133" s="4" t="inlineStr"/>
+      <c r="AY133" s="4" t="inlineStr"/>
+      <c r="AZ133" s="4" t="inlineStr"/>
+      <c r="BA133" s="4" t="inlineStr"/>
+      <c r="BB133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -31809,6 +32499,11 @@
       </c>
       <c r="AV134" s="2" t="inlineStr"/>
       <c r="AW134" s="2" t="inlineStr"/>
+      <c r="AX134" s="2" t="inlineStr"/>
+      <c r="AY134" s="2" t="inlineStr"/>
+      <c r="AZ134" s="2" t="inlineStr"/>
+      <c r="BA134" s="2" t="inlineStr"/>
+      <c r="BB134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -32041,6 +32736,11 @@
       </c>
       <c r="AV135" s="4" t="inlineStr"/>
       <c r="AW135" s="4" t="inlineStr"/>
+      <c r="AX135" s="4" t="inlineStr"/>
+      <c r="AY135" s="4" t="inlineStr"/>
+      <c r="AZ135" s="4" t="inlineStr"/>
+      <c r="BA135" s="4" t="inlineStr"/>
+      <c r="BB135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -32264,6 +32964,11 @@
       </c>
       <c r="AV136" s="2" t="inlineStr"/>
       <c r="AW136" s="2" t="inlineStr"/>
+      <c r="AX136" s="2" t="inlineStr"/>
+      <c r="AY136" s="2" t="inlineStr"/>
+      <c r="AZ136" s="2" t="inlineStr"/>
+      <c r="BA136" s="2" t="inlineStr"/>
+      <c r="BB136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -32483,6 +33188,11 @@
       </c>
       <c r="AV137" s="4" t="inlineStr"/>
       <c r="AW137" s="4" t="inlineStr"/>
+      <c r="AX137" s="4" t="inlineStr"/>
+      <c r="AY137" s="4" t="inlineStr"/>
+      <c r="AZ137" s="4" t="inlineStr"/>
+      <c r="BA137" s="4" t="inlineStr"/>
+      <c r="BB137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -32719,6 +33429,11 @@
       </c>
       <c r="AV138" s="2" t="inlineStr"/>
       <c r="AW138" s="2" t="inlineStr"/>
+      <c r="AX138" s="2" t="inlineStr"/>
+      <c r="AY138" s="2" t="inlineStr"/>
+      <c r="AZ138" s="2" t="inlineStr"/>
+      <c r="BA138" s="2" t="inlineStr"/>
+      <c r="BB138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -32954,6 +33669,11 @@
           <t>https://web.microsoftstream.com/video/6e74c0e2-b2c6-4bd6-9b53-5982d3f1b8e1?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX139" s="4" t="inlineStr"/>
+      <c r="AY139" s="4" t="inlineStr"/>
+      <c r="AZ139" s="4" t="inlineStr"/>
+      <c r="BA139" s="4" t="inlineStr"/>
+      <c r="BB139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -33185,6 +33905,11 @@
       </c>
       <c r="AV140" s="2" t="inlineStr"/>
       <c r="AW140" s="2" t="inlineStr"/>
+      <c r="AX140" s="2" t="inlineStr"/>
+      <c r="AY140" s="2" t="inlineStr"/>
+      <c r="AZ140" s="2" t="inlineStr"/>
+      <c r="BA140" s="2" t="inlineStr"/>
+      <c r="BB140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -33420,6 +34145,11 @@
           <t>https://web.microsoftstream.com/video/b2ec8a38-dced-4be0-9b7d-e8ceaec2a86e?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX141" s="4" t="inlineStr"/>
+      <c r="AY141" s="4" t="inlineStr"/>
+      <c r="AZ141" s="4" t="inlineStr"/>
+      <c r="BA141" s="4" t="inlineStr"/>
+      <c r="BB141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -33654,6 +34384,11 @@
       </c>
       <c r="AV142" s="2" t="inlineStr"/>
       <c r="AW142" s="2" t="inlineStr"/>
+      <c r="AX142" s="2" t="inlineStr"/>
+      <c r="AY142" s="2" t="inlineStr"/>
+      <c r="AZ142" s="2" t="inlineStr"/>
+      <c r="BA142" s="2" t="inlineStr"/>
+      <c r="BB142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -33888,6 +34623,11 @@
       </c>
       <c r="AV143" s="4" t="inlineStr"/>
       <c r="AW143" s="4" t="inlineStr"/>
+      <c r="AX143" s="4" t="inlineStr"/>
+      <c r="AY143" s="4" t="inlineStr"/>
+      <c r="AZ143" s="4" t="inlineStr"/>
+      <c r="BA143" s="4" t="inlineStr"/>
+      <c r="BB143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -34124,6 +34864,11 @@
       </c>
       <c r="AV144" s="2" t="inlineStr"/>
       <c r="AW144" s="2" t="inlineStr"/>
+      <c r="AX144" s="2" t="inlineStr"/>
+      <c r="AY144" s="2" t="inlineStr"/>
+      <c r="AZ144" s="2" t="inlineStr"/>
+      <c r="BA144" s="2" t="inlineStr"/>
+      <c r="BB144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -34363,6 +35108,11 @@
           <t>https://web.microsoftstream.com/video/40583c46-21c1-4547-8443-856ee5a2beb3?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX145" s="4" t="inlineStr"/>
+      <c r="AY145" s="4" t="inlineStr"/>
+      <c r="AZ145" s="4" t="inlineStr"/>
+      <c r="BA145" s="4" t="inlineStr"/>
+      <c r="BB145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -34603,6 +35353,11 @@
           <t>https://web.microsoftstream.com/video/95da0d56-cc06-4781-a262-9d91a3e9b48d?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX146" s="2" t="inlineStr"/>
+      <c r="AY146" s="2" t="inlineStr"/>
+      <c r="AZ146" s="2" t="inlineStr"/>
+      <c r="BA146" s="2" t="inlineStr"/>
+      <c r="BB146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -34834,6 +35589,11 @@
       </c>
       <c r="AV147" s="4" t="inlineStr"/>
       <c r="AW147" s="4" t="inlineStr"/>
+      <c r="AX147" s="4" t="inlineStr"/>
+      <c r="AY147" s="4" t="inlineStr"/>
+      <c r="AZ147" s="4" t="inlineStr"/>
+      <c r="BA147" s="4" t="inlineStr"/>
+      <c r="BB147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -35069,6 +35829,11 @@
       </c>
       <c r="AV148" s="2" t="inlineStr"/>
       <c r="AW148" s="2" t="inlineStr"/>
+      <c r="AX148" s="2" t="inlineStr"/>
+      <c r="AY148" s="2" t="inlineStr"/>
+      <c r="AZ148" s="2" t="inlineStr"/>
+      <c r="BA148" s="2" t="inlineStr"/>
+      <c r="BB148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -35311,6 +36076,11 @@
           <t>https://web.microsoftstream.com/video/e092ed57-1ff7-4570-9897-57fc78b1a0c8?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX149" s="4" t="inlineStr"/>
+      <c r="AY149" s="4" t="inlineStr"/>
+      <c r="AZ149" s="4" t="inlineStr"/>
+      <c r="BA149" s="4" t="inlineStr"/>
+      <c r="BB149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -35549,6 +36319,11 @@
       </c>
       <c r="AV150" s="2" t="inlineStr"/>
       <c r="AW150" s="2" t="inlineStr"/>
+      <c r="AX150" s="2" t="inlineStr"/>
+      <c r="AY150" s="2" t="inlineStr"/>
+      <c r="AZ150" s="2" t="inlineStr"/>
+      <c r="BA150" s="2" t="inlineStr"/>
+      <c r="BB150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -35791,6 +36566,11 @@
           <t>https://web.microsoftstream.com/video/e092ed57-1ff7-4570-9897-57fc78b1a0c8?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX151" s="4" t="inlineStr"/>
+      <c r="AY151" s="4" t="inlineStr"/>
+      <c r="AZ151" s="4" t="inlineStr"/>
+      <c r="BA151" s="4" t="inlineStr"/>
+      <c r="BB151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -36022,6 +36802,11 @@
       </c>
       <c r="AV152" s="2" t="inlineStr"/>
       <c r="AW152" s="2" t="inlineStr"/>
+      <c r="AX152" s="2" t="inlineStr"/>
+      <c r="AY152" s="2" t="inlineStr"/>
+      <c r="AZ152" s="2" t="inlineStr"/>
+      <c r="BA152" s="2" t="inlineStr"/>
+      <c r="BB152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -36253,6 +37038,11 @@
       </c>
       <c r="AV153" s="4" t="inlineStr"/>
       <c r="AW153" s="4" t="inlineStr"/>
+      <c r="AX153" s="4" t="inlineStr"/>
+      <c r="AY153" s="4" t="inlineStr"/>
+      <c r="AZ153" s="4" t="inlineStr"/>
+      <c r="BA153" s="4" t="inlineStr"/>
+      <c r="BB153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -36490,6 +37280,11 @@
       </c>
       <c r="AV154" s="2" t="inlineStr"/>
       <c r="AW154" s="2" t="inlineStr"/>
+      <c r="AX154" s="2" t="inlineStr"/>
+      <c r="AY154" s="2" t="inlineStr"/>
+      <c r="AZ154" s="2" t="inlineStr"/>
+      <c r="BA154" s="2" t="inlineStr"/>
+      <c r="BB154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -36585,6 +37380,11 @@
       <c r="AU155" s="4" t="inlineStr"/>
       <c r="AV155" s="4" t="inlineStr"/>
       <c r="AW155" s="4" t="inlineStr"/>
+      <c r="AX155" s="4" t="inlineStr"/>
+      <c r="AY155" s="4" t="inlineStr"/>
+      <c r="AZ155" s="4" t="inlineStr"/>
+      <c r="BA155" s="4" t="inlineStr"/>
+      <c r="BB155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -36816,6 +37616,11 @@
       </c>
       <c r="AV156" s="2" t="inlineStr"/>
       <c r="AW156" s="2" t="inlineStr"/>
+      <c r="AX156" s="2" t="inlineStr"/>
+      <c r="AY156" s="2" t="inlineStr"/>
+      <c r="AZ156" s="2" t="inlineStr"/>
+      <c r="BA156" s="2" t="inlineStr"/>
+      <c r="BB156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -37058,6 +37863,11 @@
           <t>https://web.microsoftstream.com/video/e092ed57-1ff7-4570-9897-57fc78b1a0c8?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX157" s="4" t="inlineStr"/>
+      <c r="AY157" s="4" t="inlineStr"/>
+      <c r="AZ157" s="4" t="inlineStr"/>
+      <c r="BA157" s="4" t="inlineStr"/>
+      <c r="BB157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -37297,6 +38107,11 @@
           <t>https://web.microsoftstream.com/video/91aaf70b-85c2-4cf1-b537-e42b3bd894ec?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX158" s="2" t="inlineStr"/>
+      <c r="AY158" s="2" t="inlineStr"/>
+      <c r="AZ158" s="2" t="inlineStr"/>
+      <c r="BA158" s="2" t="inlineStr"/>
+      <c r="BB158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -37532,6 +38347,11 @@
       </c>
       <c r="AV159" s="4" t="inlineStr"/>
       <c r="AW159" s="4" t="inlineStr"/>
+      <c r="AX159" s="4" t="inlineStr"/>
+      <c r="AY159" s="4" t="inlineStr"/>
+      <c r="AZ159" s="4" t="inlineStr"/>
+      <c r="BA159" s="4" t="inlineStr"/>
+      <c r="BB159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -37763,6 +38583,11 @@
       </c>
       <c r="AV160" s="2" t="inlineStr"/>
       <c r="AW160" s="2" t="inlineStr"/>
+      <c r="AX160" s="2" t="inlineStr"/>
+      <c r="AY160" s="2" t="inlineStr"/>
+      <c r="AZ160" s="2" t="inlineStr"/>
+      <c r="BA160" s="2" t="inlineStr"/>
+      <c r="BB160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -37996,6 +38821,11 @@
       </c>
       <c r="AV161" s="4" t="inlineStr"/>
       <c r="AW161" s="4" t="inlineStr"/>
+      <c r="AX161" s="4" t="inlineStr"/>
+      <c r="AY161" s="4" t="inlineStr"/>
+      <c r="AZ161" s="4" t="inlineStr"/>
+      <c r="BA161" s="4" t="inlineStr"/>
+      <c r="BB161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -38091,6 +38921,11 @@
       <c r="AU162" s="2" t="inlineStr"/>
       <c r="AV162" s="2" t="inlineStr"/>
       <c r="AW162" s="2" t="inlineStr"/>
+      <c r="AX162" s="2" t="inlineStr"/>
+      <c r="AY162" s="2" t="inlineStr"/>
+      <c r="AZ162" s="2" t="inlineStr"/>
+      <c r="BA162" s="2" t="inlineStr"/>
+      <c r="BB162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -38327,6 +39162,11 @@
       </c>
       <c r="AV163" s="4" t="inlineStr"/>
       <c r="AW163" s="4" t="inlineStr"/>
+      <c r="AX163" s="4" t="inlineStr"/>
+      <c r="AY163" s="4" t="inlineStr"/>
+      <c r="AZ163" s="4" t="inlineStr"/>
+      <c r="BA163" s="4" t="inlineStr"/>
+      <c r="BB163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -38554,6 +39394,11 @@
       </c>
       <c r="AV164" s="2" t="inlineStr"/>
       <c r="AW164" s="2" t="inlineStr"/>
+      <c r="AX164" s="2" t="inlineStr"/>
+      <c r="AY164" s="2" t="inlineStr"/>
+      <c r="AZ164" s="2" t="inlineStr"/>
+      <c r="BA164" s="2" t="inlineStr"/>
+      <c r="BB164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -38785,6 +39630,11 @@
       </c>
       <c r="AV165" s="4" t="inlineStr"/>
       <c r="AW165" s="4" t="inlineStr"/>
+      <c r="AX165" s="4" t="inlineStr"/>
+      <c r="AY165" s="4" t="inlineStr"/>
+      <c r="AZ165" s="4" t="inlineStr"/>
+      <c r="BA165" s="4" t="inlineStr"/>
+      <c r="BB165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -39020,6 +39870,11 @@
       </c>
       <c r="AV166" s="2" t="inlineStr"/>
       <c r="AW166" s="2" t="inlineStr"/>
+      <c r="AX166" s="2" t="inlineStr"/>
+      <c r="AY166" s="2" t="inlineStr"/>
+      <c r="AZ166" s="2" t="inlineStr"/>
+      <c r="BA166" s="2" t="inlineStr"/>
+      <c r="BB166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -39255,6 +40110,11 @@
           <t>https://web.microsoftstream.com/video/d81cd129-394e-4fda-99cf-dd88633d940f?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
         </is>
       </c>
+      <c r="AX167" s="4" t="inlineStr"/>
+      <c r="AY167" s="4" t="inlineStr"/>
+      <c r="AZ167" s="4" t="inlineStr"/>
+      <c r="BA167" s="4" t="inlineStr"/>
+      <c r="BB167" s="4" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -39486,6 +40346,11 @@
       </c>
       <c r="AV168" s="2" t="inlineStr"/>
       <c r="AW168" s="2" t="inlineStr"/>
+      <c r="AX168" s="2" t="inlineStr"/>
+      <c r="AY168" s="2" t="inlineStr"/>
+      <c r="AZ168" s="2" t="inlineStr"/>
+      <c r="BA168" s="2" t="inlineStr"/>
+      <c r="BB168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -39721,6 +40586,11 @@
       </c>
       <c r="AV169" s="4" t="inlineStr"/>
       <c r="AW169" s="4" t="inlineStr"/>
+      <c r="AX169" s="4" t="inlineStr"/>
+      <c r="AY169" s="4" t="inlineStr"/>
+      <c r="AZ169" s="4" t="inlineStr"/>
+      <c r="BA169" s="4" t="inlineStr"/>
+      <c r="BB169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -39948,6 +40818,11 @@
       </c>
       <c r="AV170" s="2" t="inlineStr"/>
       <c r="AW170" s="2" t="inlineStr"/>
+      <c r="AX170" s="2" t="inlineStr"/>
+      <c r="AY170" s="2" t="inlineStr"/>
+      <c r="AZ170" s="2" t="inlineStr"/>
+      <c r="BA170" s="2" t="inlineStr"/>
+      <c r="BB170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -40175,6 +41050,11 @@
       </c>
       <c r="AV171" s="4" t="inlineStr"/>
       <c r="AW171" s="4" t="inlineStr"/>
+      <c r="AX171" s="4" t="inlineStr"/>
+      <c r="AY171" s="4" t="inlineStr"/>
+      <c r="AZ171" s="4" t="inlineStr"/>
+      <c r="BA171" s="4" t="inlineStr"/>
+      <c r="BB171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -40402,6 +41282,11 @@
       </c>
       <c r="AV172" s="2" t="inlineStr"/>
       <c r="AW172" s="2" t="inlineStr"/>
+      <c r="AX172" s="2" t="inlineStr"/>
+      <c r="AY172" s="2" t="inlineStr"/>
+      <c r="AZ172" s="2" t="inlineStr"/>
+      <c r="BA172" s="2" t="inlineStr"/>
+      <c r="BB172" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
